--- a/comparativa_300_vs_1000.xlsx
+++ b/comparativa_300_vs_1000.xlsx
@@ -1,34 +1,89 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Proyectos\entrega-simulador-pac-2028\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{580BD98E-9452-4810-B893-82FA75760A87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="2430" yWindow="9068" windowWidth="28800" windowHeight="13747" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Comparativa_300_vs_1000" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Comparativa_300_vs_1000" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="11">
+  <si>
+    <t>CUADRO 1 — Nº de beneficiarios (simulado)</t>
+  </si>
+  <si>
+    <t>Territorio</t>
+  </si>
+  <si>
+    <t>&gt;300 €</t>
+  </si>
+  <si>
+    <t>&gt;1000 €</t>
+  </si>
+  <si>
+    <t>Araba</t>
+  </si>
+  <si>
+    <t>Gipuzkoa</t>
+  </si>
+  <si>
+    <t>Bizkaia</t>
+  </si>
+  <si>
+    <t>Euskadi</t>
+  </si>
+  <si>
+    <t>CUADRO 2 — Superficie activada (ha) (simulado)</t>
+  </si>
+  <si>
+    <t>CUADRO 3 — Importe medio por explotación (€) (simulado)</t>
+  </si>
+  <si>
+    <t>Diferencia (&gt;1000 − &gt;300)</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -47,80 +102,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -408,291 +404,245 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D20"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.06640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>CUADRO 1 — Nº de beneficiarios (simulado)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Territorio</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>&gt;300 €</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>&gt;1000 €</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Diferencia (&gt;300 − &gt;1000)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Araba</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3">
         <v>1518</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C3">
         <v>1399</v>
       </c>
-      <c r="D3" t="n">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Gipuzkoa</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
+      <c r="D3">
+        <f>C3-B3</f>
+        <v>-119</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4">
         <v>2634</v>
       </c>
-      <c r="C4" t="n">
+      <c r="C4">
         <v>1756</v>
       </c>
-      <c r="D4" t="n">
-        <v>878</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Bizkaia</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
+      <c r="D4">
+        <f t="shared" ref="D4:D6" si="0">C4-B4</f>
+        <v>-878</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5">
         <v>2181</v>
       </c>
-      <c r="C5" t="n">
+      <c r="C5">
         <v>1270</v>
       </c>
-      <c r="D5" t="n">
-        <v>911</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Euskadi</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
+      <c r="D5">
+        <f t="shared" si="0"/>
+        <v>-911</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6">
         <v>6333</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C6">
         <v>4425</v>
       </c>
-      <c r="D6" t="n">
-        <v>1908</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>CUADRO 2 — Superficie activada (ha) (simulado)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Territorio</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>&gt;300 €</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>&gt;1000 €</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Diferencia (&gt;300 − &gt;1000)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Araba</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
+      <c r="D6">
+        <f t="shared" si="0"/>
+        <v>-1908</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A9" t="s">
+        <v>1</v>
+      </c>
+      <c r="B9" t="s">
+        <v>2</v>
+      </c>
+      <c r="C9" t="s">
+        <v>3</v>
+      </c>
+      <c r="D9" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B10">
         <v>94487.59</v>
       </c>
-      <c r="C10" t="n">
-        <v>93827.96000000001</v>
-      </c>
-      <c r="D10" t="n">
-        <v>659.63</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Gipuzkoa</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
+      <c r="C10">
+        <v>93827.96</v>
+      </c>
+      <c r="D10">
+        <f>C10-B10</f>
+        <v>-659.6299999999901</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A11" t="s">
+        <v>5</v>
+      </c>
+      <c r="B11">
         <v>30734.97</v>
       </c>
-      <c r="C11" t="n">
+      <c r="C11">
         <v>28029.47</v>
       </c>
-      <c r="D11" t="n">
-        <v>2705.5</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Bizkaia</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
+      <c r="D11">
+        <f t="shared" ref="D11:D13" si="1">C11-B11</f>
+        <v>-2705.5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A12" t="s">
+        <v>6</v>
+      </c>
+      <c r="B12">
         <v>27781.65</v>
       </c>
-      <c r="C12" t="n">
+      <c r="C12">
         <v>24893.68</v>
       </c>
-      <c r="D12" t="n">
-        <v>2887.97</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Euskadi</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
+      <c r="D12">
+        <f t="shared" si="1"/>
+        <v>-2887.9700000000012</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A13" t="s">
+        <v>7</v>
+      </c>
+      <c r="B13">
         <v>153004.21</v>
       </c>
-      <c r="C13" t="n">
-        <v>146751.11</v>
-      </c>
-      <c r="D13" t="n">
-        <v>6253.1</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>CUADRO 3 — Importe medio por explotación (€) (simulado)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Territorio</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>&gt;300 €</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>&gt;1000 €</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Diferencia (&gt;300 − &gt;1000)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Araba</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>17229.99</v>
-      </c>
-      <c r="C17" t="n">
+      <c r="C13">
+        <v>146751.10999999999</v>
+      </c>
+      <c r="D13">
+        <f t="shared" si="1"/>
+        <v>-6253.1000000000058</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A15" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A16" t="s">
+        <v>1</v>
+      </c>
+      <c r="B16" t="s">
+        <v>2</v>
+      </c>
+      <c r="C16" t="s">
+        <v>3</v>
+      </c>
+      <c r="D16" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A17" t="s">
+        <v>4</v>
+      </c>
+      <c r="B17">
+        <v>17229.990000000002</v>
+      </c>
+      <c r="C17">
         <v>19356.13</v>
       </c>
-      <c r="D17" t="n">
-        <v>-2126.14</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Gipuzkoa</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
+      <c r="D17">
+        <f>C17-B17</f>
+        <v>2126.1399999999994</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A18" t="s">
+        <v>5</v>
+      </c>
+      <c r="B18">
         <v>3229.97</v>
       </c>
-      <c r="C18" t="n">
+      <c r="C18">
         <v>4606.75</v>
       </c>
-      <c r="D18" t="n">
-        <v>-1376.78</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Bizkaia</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
+      <c r="D18">
+        <f t="shared" ref="D18:D20" si="2">C18-B18</f>
+        <v>1376.7800000000002</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A19" t="s">
+        <v>6</v>
+      </c>
+      <c r="B19">
         <v>3526.02</v>
       </c>
-      <c r="C19" t="n">
+      <c r="C19">
         <v>5657.04</v>
       </c>
-      <c r="D19" t="n">
-        <v>-2131.02</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Euskadi</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
+      <c r="D19">
+        <f t="shared" si="2"/>
+        <v>2131.02</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A20" t="s">
+        <v>7</v>
+      </c>
+      <c r="B20">
         <v>6687.69</v>
       </c>
-      <c r="C20" t="n">
+      <c r="C20">
         <v>9571.33</v>
       </c>
-      <c r="D20" t="n">
-        <v>-2883.64</v>
+      <c r="D20">
+        <f t="shared" si="2"/>
+        <v>2883.6400000000003</v>
       </c>
     </row>
   </sheetData>

--- a/comparativa_300_vs_1000.xlsx
+++ b/comparativa_300_vs_1000.xlsx
@@ -1,89 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Proyectos\entrega-simulador-pac-2028\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{580BD98E-9452-4810-B893-82FA75760A87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="2430" yWindow="9068" windowWidth="28800" windowHeight="13747" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Comparativa_300_vs_1000" sheetId="1" r:id="rId1"/>
+    <sheet name="Comparativa_300_vs_1000" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="11">
-  <si>
-    <t>CUADRO 1 — Nº de beneficiarios (simulado)</t>
-  </si>
-  <si>
-    <t>Territorio</t>
-  </si>
-  <si>
-    <t>&gt;300 €</t>
-  </si>
-  <si>
-    <t>&gt;1000 €</t>
-  </si>
-  <si>
-    <t>Araba</t>
-  </si>
-  <si>
-    <t>Gipuzkoa</t>
-  </si>
-  <si>
-    <t>Bizkaia</t>
-  </si>
-  <si>
-    <t>Euskadi</t>
-  </si>
-  <si>
-    <t>CUADRO 2 — Superficie activada (ha) (simulado)</t>
-  </si>
-  <si>
-    <t>CUADRO 3 — Importe medio por explotación (€) (simulado)</t>
-  </si>
-  <si>
-    <t>Diferencia (&gt;1000 − &gt;300)</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -102,21 +47,80 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -404,245 +408,291 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:D20"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.06640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3">
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>CUADRO 1 — Nº de beneficiarios (simulado)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Territorio</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>&gt;300 €</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>&gt;1000 €</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Diferencia (&gt;300 − &gt;1000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Araba</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
         <v>1518</v>
       </c>
-      <c r="C3">
+      <c r="C3" t="n">
         <v>1399</v>
       </c>
-      <c r="D3">
-        <f>C3-B3</f>
-        <v>-119</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4">
+      <c r="D3" t="n">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Gipuzkoa</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
         <v>2634</v>
       </c>
-      <c r="C4">
+      <c r="C4" t="n">
         <v>1756</v>
       </c>
-      <c r="D4">
-        <f t="shared" ref="D4:D6" si="0">C4-B4</f>
-        <v>-878</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5">
+      <c r="D4" t="n">
+        <v>878</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Bizkaia</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
         <v>2181</v>
       </c>
-      <c r="C5">
+      <c r="C5" t="n">
         <v>1270</v>
       </c>
-      <c r="D5">
-        <f t="shared" si="0"/>
-        <v>-911</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6">
+      <c r="D5" t="n">
+        <v>911</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Euskadi</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
         <v>6333</v>
       </c>
-      <c r="C6">
+      <c r="C6" t="n">
         <v>4425</v>
       </c>
-      <c r="D6">
-        <f t="shared" si="0"/>
-        <v>-1908</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A8" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A9" t="s">
-        <v>1</v>
-      </c>
-      <c r="B9" t="s">
-        <v>2</v>
-      </c>
-      <c r="C9" t="s">
-        <v>3</v>
-      </c>
-      <c r="D9" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A10" t="s">
-        <v>4</v>
-      </c>
-      <c r="B10">
-        <v>94487.59</v>
-      </c>
-      <c r="C10">
-        <v>93827.96</v>
-      </c>
-      <c r="D10">
-        <f>C10-B10</f>
-        <v>-659.6299999999901</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A11" t="s">
-        <v>5</v>
-      </c>
-      <c r="B11">
-        <v>30734.97</v>
-      </c>
-      <c r="C11">
-        <v>28029.47</v>
-      </c>
-      <c r="D11">
-        <f t="shared" ref="D11:D13" si="1">C11-B11</f>
-        <v>-2705.5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A12" t="s">
-        <v>6</v>
-      </c>
-      <c r="B12">
-        <v>27781.65</v>
-      </c>
-      <c r="C12">
-        <v>24893.68</v>
-      </c>
-      <c r="D12">
-        <f t="shared" si="1"/>
-        <v>-2887.9700000000012</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A13" t="s">
-        <v>7</v>
-      </c>
-      <c r="B13">
-        <v>153004.21</v>
-      </c>
-      <c r="C13">
-        <v>146751.10999999999</v>
-      </c>
-      <c r="D13">
-        <f t="shared" si="1"/>
-        <v>-6253.1000000000058</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A15" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A16" t="s">
-        <v>1</v>
-      </c>
-      <c r="B16" t="s">
-        <v>2</v>
-      </c>
-      <c r="C16" t="s">
-        <v>3</v>
-      </c>
-      <c r="D16" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A17" t="s">
-        <v>4</v>
-      </c>
-      <c r="B17">
-        <v>17229.990000000002</v>
-      </c>
-      <c r="C17">
-        <v>19356.13</v>
-      </c>
-      <c r="D17">
-        <f>C17-B17</f>
-        <v>2126.1399999999994</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A18" t="s">
-        <v>5</v>
-      </c>
-      <c r="B18">
-        <v>3229.97</v>
-      </c>
-      <c r="C18">
-        <v>4606.75</v>
-      </c>
-      <c r="D18">
-        <f t="shared" ref="D18:D20" si="2">C18-B18</f>
-        <v>1376.7800000000002</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A19" t="s">
-        <v>6</v>
-      </c>
-      <c r="B19">
-        <v>3526.02</v>
-      </c>
-      <c r="C19">
-        <v>5657.04</v>
-      </c>
-      <c r="D19">
-        <f t="shared" si="2"/>
-        <v>2131.02</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A20" t="s">
-        <v>7</v>
-      </c>
-      <c r="B20">
+      <c r="D6" t="n">
+        <v>1908</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>CUADRO 2 — Superficie activada (ha) (simulado)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Territorio</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>&gt;300 €</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>&gt;1000 €</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Diferencia (&gt;300 − &gt;1000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Araba</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>87830.17999999999</v>
+      </c>
+      <c r="C10" t="n">
+        <v>87254.37</v>
+      </c>
+      <c r="D10" t="n">
+        <v>575.8099999999999</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Gipuzkoa</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>27318</v>
+      </c>
+      <c r="C11" t="n">
+        <v>24975.33</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2342.67</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Bizkaia</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>23919.95</v>
+      </c>
+      <c r="C12" t="n">
+        <v>21505.08</v>
+      </c>
+      <c r="D12" t="n">
+        <v>2414.87</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Euskadi</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>139068.13</v>
+      </c>
+      <c r="C13" t="n">
+        <v>133734.78</v>
+      </c>
+      <c r="D13" t="n">
+        <v>5333.35</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>CUADRO 3 — Importe medio por explotación (€) (simulado)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Territorio</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>&gt;300 €</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>&gt;1000 €</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Diferencia (&gt;300 − &gt;1000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Araba</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>17620.97</v>
+      </c>
+      <c r="C17" t="n">
+        <v>19751.97</v>
+      </c>
+      <c r="D17" t="n">
+        <v>-2131</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Gipuzkoa</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>3158.57</v>
+      </c>
+      <c r="C18" t="n">
+        <v>4504.3</v>
+      </c>
+      <c r="D18" t="n">
+        <v>-1345.73</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Bizkaia</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>3340.12</v>
+      </c>
+      <c r="C19" t="n">
+        <v>5362.64</v>
+      </c>
+      <c r="D19" t="n">
+        <v>-2022.52</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Euskadi</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
         <v>6687.69</v>
       </c>
-      <c r="C20">
+      <c r="C20" t="n">
         <v>9571.33</v>
       </c>
-      <c r="D20">
-        <f t="shared" si="2"/>
-        <v>2883.6400000000003</v>
+      <c r="D20" t="n">
+        <v>-2883.64</v>
       </c>
     </row>
   </sheetData>
